--- a/excel_routes/route_ATZ_JED_threats.xlsx
+++ b/excel_routes/route_ATZ_JED_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -48,14 +48,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -86,9 +80,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -532,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -542,30 +533,30 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>flyadeal F3-778</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>7755</v>
+        <v>7426</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>13289</v>
+        <v>21461</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-5534</v>
+        <v>-14035</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -577,7 +568,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -587,30 +578,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-641</t>
+          <t>Nile Air NP-227</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7755</v>
+        <v>10048</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>13289</v>
+        <v>21461</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-5534</v>
+        <v>-11413</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -622,7 +613,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -632,30 +623,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>7755</v>
+        <v>10048</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>13289</v>
+        <v>21461</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-5534</v>
+        <v>-11413</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -667,7 +658,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -677,30 +668,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>flyadeal F3-754</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>4954</v>
+        <v>11863</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>8818</v>
+        <v>21461</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-3864</v>
+        <v>-9598</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -712,7 +703,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -722,17 +713,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-641</t>
+          <t>Saudia SV-6898</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>7286</v>
+        <v>11986</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>8818</v>
+        <v>21461</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-1532</v>
+        <v>-9475</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>46</v>
@@ -743,9 +734,9 @@
       <c r="I6" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">

--- a/excel_routes/route_ATZ_JED_threats.xlsx
+++ b/excel_routes/route_ATZ_JED_threats.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_260726_at_14.46\reports\excel_routes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_270726_at_12.25\reports\excel_routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81A21EE2-7842-4091-BCDC-9E8C8191E9CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EBC6A22-3280-4EA4-AB9F-EA6F08BE6620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12972" yWindow="348" windowWidth="10068" windowHeight="10284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="46">
   <si>
     <t>Date</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Currency</t>
   </si>
   <si>
-    <t>05-AUG-26</t>
+    <t>19-AUG-26</t>
   </si>
   <si>
     <t>SM-455</t>
@@ -69,78 +69,60 @@
     <t>flyadeal F3-778</t>
   </si>
   <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>EGP</t>
+  </si>
+  <si>
+    <t>23-AUG-26</t>
+  </si>
+  <si>
+    <t>05-SEP-26</t>
+  </si>
+  <si>
+    <t>SM-983</t>
+  </si>
+  <si>
+    <t>EgyptAir MS-673</t>
+  </si>
+  <si>
+    <t>EgyptAir MS-663</t>
+  </si>
+  <si>
+    <t>11-SEP-26</t>
+  </si>
+  <si>
+    <t>EgyptAir MS-671</t>
+  </si>
+  <si>
+    <t>13-SEP-26</t>
+  </si>
+  <si>
+    <t>Saudia SV-6898</t>
+  </si>
+  <si>
+    <t>16-SEP-26</t>
+  </si>
+  <si>
+    <t>20-SEP-26</t>
+  </si>
+  <si>
+    <t>27-SEP-26</t>
+  </si>
+  <si>
+    <t>30-SEP-26</t>
+  </si>
+  <si>
+    <t>01-OCT-26</t>
+  </si>
+  <si>
+    <t>SM-959</t>
+  </si>
+  <si>
     <t>HIGH</t>
   </si>
   <si>
-    <t>EGP</t>
-  </si>
-  <si>
-    <t>Nile Air NP-127</t>
-  </si>
-  <si>
-    <t>flyadeal F3-754</t>
-  </si>
-  <si>
-    <t>flyadeal F3-764</t>
-  </si>
-  <si>
-    <t>Saudia SV-6898</t>
-  </si>
-  <si>
-    <t>12-AUG-26</t>
-  </si>
-  <si>
-    <t>LOW</t>
-  </si>
-  <si>
-    <t>19-AUG-26</t>
-  </si>
-  <si>
-    <t>26-AUG-26</t>
-  </si>
-  <si>
-    <t>30-AUG-26</t>
-  </si>
-  <si>
-    <t>05-SEP-26</t>
-  </si>
-  <si>
-    <t>SM-983</t>
-  </si>
-  <si>
-    <t>EgyptAir MS-673</t>
-  </si>
-  <si>
-    <t>EgyptAir MS-663</t>
-  </si>
-  <si>
-    <t>11-SEP-26</t>
-  </si>
-  <si>
-    <t>EgyptAir MS-671</t>
-  </si>
-  <si>
-    <t>13-SEP-26</t>
-  </si>
-  <si>
-    <t>16-SEP-26</t>
-  </si>
-  <si>
-    <t>20-SEP-26</t>
-  </si>
-  <si>
-    <t>27-SEP-26</t>
-  </si>
-  <si>
-    <t>30-SEP-26</t>
-  </si>
-  <si>
-    <t>01-OCT-26</t>
-  </si>
-  <si>
-    <t>SM-959</t>
-  </si>
-  <si>
     <t>EgyptAir MS-643</t>
   </si>
   <si>
@@ -156,19 +138,25 @@
     <t>08-OCT-26</t>
   </si>
   <si>
+    <t>flynas XY-590</t>
+  </si>
+  <si>
+    <t>EgyptAir MS-661</t>
+  </si>
+  <si>
     <t>11-OCT-26</t>
   </si>
   <si>
     <t>15-OCT-26</t>
   </si>
   <si>
+    <t>flynas XY-584</t>
+  </si>
+  <si>
     <t>18-OCT-26</t>
   </si>
   <si>
     <t>22-OCT-26</t>
-  </si>
-  <si>
-    <t>EgyptAir MS-661</t>
   </si>
   <si>
     <t>07-DEC-26</t>
@@ -216,14 +204,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor rgb="FFF8D7DA"/>
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor rgb="FFD4EDDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor rgb="FFD4EDDA"/>
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor rgb="FFF8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -571,7 +559,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -632,13 +620,13 @@
         <v>13</v>
       </c>
       <c r="D2" s="2">
-        <v>8587</v>
+        <v>4901</v>
       </c>
       <c r="E2" s="2">
-        <v>21461</v>
+        <v>9433</v>
       </c>
       <c r="F2" s="2">
-        <v>-12874</v>
+        <v>-4532</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -658,31 +646,31 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D3" s="2">
-        <v>10444</v>
+        <v>4901</v>
       </c>
       <c r="E3" s="2">
-        <v>21461</v>
+        <v>9433</v>
       </c>
       <c r="F3" s="2">
-        <v>-11017</v>
+        <v>-4532</v>
       </c>
       <c r="G3" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H3" s="2">
         <v>30</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>14</v>
@@ -693,31 +681,31 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D4" s="2">
-        <v>11863</v>
+        <v>8095</v>
       </c>
       <c r="E4" s="2">
-        <v>21461</v>
+        <v>8778</v>
       </c>
       <c r="F4" s="2">
-        <v>-9598</v>
+        <v>-683</v>
       </c>
       <c r="G4" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H4" s="2">
         <v>30</v>
       </c>
       <c r="I4" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>14</v>
@@ -728,31 +716,31 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2">
-        <v>12136</v>
+        <v>8095</v>
       </c>
       <c r="E5" s="2">
-        <v>21461</v>
+        <v>8778</v>
       </c>
       <c r="F5" s="2">
-        <v>-9325</v>
+        <v>-683</v>
       </c>
       <c r="G5" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H5" s="2">
         <v>30</v>
       </c>
       <c r="I5" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>14</v>
@@ -763,22 +751,22 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D6" s="2">
-        <v>15276</v>
+        <v>8095</v>
       </c>
       <c r="E6" s="2">
-        <v>21461</v>
+        <v>8778</v>
       </c>
       <c r="F6" s="2">
-        <v>-6185</v>
+        <v>-683</v>
       </c>
       <c r="G6" s="2">
         <v>46</v>
@@ -798,34 +786,34 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D7" s="2">
-        <v>4901</v>
+        <v>10252</v>
       </c>
       <c r="E7" s="2">
-        <v>9433</v>
+        <v>8286</v>
       </c>
       <c r="F7" s="2">
-        <v>-4532</v>
+        <v>1966</v>
       </c>
       <c r="G7" s="2">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H7" s="2">
         <v>30</v>
       </c>
       <c r="I7" s="2">
-        <v>30</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>21</v>
+        <v>-16</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>15</v>
@@ -833,34 +821,34 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D8" s="2">
-        <v>4901</v>
+        <v>9583</v>
       </c>
       <c r="E8" s="2">
-        <v>9433</v>
+        <v>8286</v>
       </c>
       <c r="F8" s="2">
-        <v>-4532</v>
+        <v>1297</v>
       </c>
       <c r="G8" s="2">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H8" s="2">
         <v>30</v>
       </c>
       <c r="I8" s="2">
-        <v>30</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>21</v>
+        <v>-16</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>15</v>
@@ -868,34 +856,34 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D9" s="2">
-        <v>5925</v>
+        <v>9583</v>
       </c>
       <c r="E9" s="2">
-        <v>7809</v>
+        <v>8286</v>
       </c>
       <c r="F9" s="2">
-        <v>-1884</v>
+        <v>1297</v>
       </c>
       <c r="G9" s="2">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H9" s="2">
         <v>30</v>
       </c>
       <c r="I9" s="2">
-        <v>10</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>21</v>
+        <v>-16</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>15</v>
@@ -903,34 +891,34 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D10" s="2">
-        <v>5925</v>
+        <v>9583</v>
       </c>
       <c r="E10" s="2">
-        <v>7809</v>
+        <v>8286</v>
       </c>
       <c r="F10" s="2">
-        <v>-1884</v>
+        <v>1297</v>
       </c>
       <c r="G10" s="2">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H10" s="2">
         <v>30</v>
       </c>
       <c r="I10" s="2">
-        <v>10</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>21</v>
+        <v>-16</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>15</v>
@@ -938,22 +926,22 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D11" s="2">
-        <v>8095</v>
+        <v>9583</v>
       </c>
       <c r="E11" s="2">
-        <v>8778</v>
+        <v>8286</v>
       </c>
       <c r="F11" s="2">
-        <v>-683</v>
+        <v>1297</v>
       </c>
       <c r="G11" s="2">
         <v>46</v>
@@ -964,8 +952,8 @@
       <c r="I11" s="2">
         <v>-16</v>
       </c>
-      <c r="J11" s="4" t="s">
-        <v>21</v>
+      <c r="J11" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>15</v>
@@ -973,34 +961,34 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D12" s="2">
-        <v>8095</v>
+        <v>6157</v>
       </c>
       <c r="E12" s="2">
-        <v>8778</v>
+        <v>21460</v>
       </c>
       <c r="F12" s="2">
-        <v>-683</v>
+        <v>-15303</v>
       </c>
       <c r="G12" s="2">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H12" s="2">
         <v>30</v>
       </c>
       <c r="I12" s="2">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>15</v>
@@ -1011,19 +999,19 @@
         <v>29</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D13" s="2">
-        <v>8095</v>
+        <v>8901</v>
       </c>
       <c r="E13" s="2">
-        <v>8778</v>
+        <v>21460</v>
       </c>
       <c r="F13" s="2">
-        <v>-683</v>
+        <v>-12559</v>
       </c>
       <c r="G13" s="2">
         <v>46</v>
@@ -1035,7 +1023,7 @@
         <v>-16</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>15</v>
@@ -1043,34 +1031,34 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="2">
+        <v>8901</v>
+      </c>
+      <c r="E14" s="2">
+        <v>21460</v>
+      </c>
+      <c r="F14" s="2">
+        <v>-12559</v>
+      </c>
+      <c r="G14" s="2">
+        <v>46</v>
+      </c>
+      <c r="H14" s="2">
+        <v>30</v>
+      </c>
+      <c r="I14" s="2">
+        <v>-16</v>
+      </c>
+      <c r="J14" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="2">
-        <v>6744</v>
-      </c>
-      <c r="E14" s="2">
-        <v>8286</v>
-      </c>
-      <c r="F14" s="2">
-        <v>-1542</v>
-      </c>
-      <c r="G14" s="2">
-        <v>20</v>
-      </c>
-      <c r="H14" s="2">
-        <v>30</v>
-      </c>
-      <c r="I14" s="2">
-        <v>10</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>21</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>15</v>
@@ -1078,22 +1066,22 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D15" s="2">
-        <v>10252</v>
+        <v>9583</v>
       </c>
       <c r="E15" s="2">
-        <v>8286</v>
+        <v>7331</v>
       </c>
       <c r="F15" s="2">
-        <v>1966</v>
+        <v>2252</v>
       </c>
       <c r="G15" s="2">
         <v>46</v>
@@ -1104,8 +1092,8 @@
       <c r="I15" s="2">
         <v>-16</v>
       </c>
-      <c r="J15" s="4" t="s">
-        <v>21</v>
+      <c r="J15" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>15</v>
@@ -1113,34 +1101,34 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="D16" s="2">
-        <v>9583</v>
+        <v>7290</v>
       </c>
       <c r="E16" s="2">
-        <v>8286</v>
+        <v>21460</v>
       </c>
       <c r="F16" s="2">
-        <v>1297</v>
+        <v>-14170</v>
       </c>
       <c r="G16" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H16" s="2">
         <v>30</v>
       </c>
       <c r="I16" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>15</v>
@@ -1148,34 +1136,34 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="D17" s="2">
-        <v>6061</v>
+        <v>8095</v>
       </c>
       <c r="E17" s="2">
-        <v>8286</v>
+        <v>21460</v>
       </c>
       <c r="F17" s="2">
-        <v>-2225</v>
+        <v>-13365</v>
       </c>
       <c r="G17" s="2">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2">
         <v>30</v>
       </c>
       <c r="I17" s="2">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>15</v>
@@ -1183,22 +1171,22 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D18" s="2">
-        <v>9583</v>
+        <v>8901</v>
       </c>
       <c r="E18" s="2">
-        <v>8286</v>
+        <v>21460</v>
       </c>
       <c r="F18" s="2">
-        <v>1297</v>
+        <v>-12559</v>
       </c>
       <c r="G18" s="2">
         <v>46</v>
@@ -1210,7 +1198,7 @@
         <v>-16</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>15</v>
@@ -1218,22 +1206,22 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D19" s="2">
         <v>9583</v>
       </c>
       <c r="E19" s="2">
-        <v>8286</v>
+        <v>7331</v>
       </c>
       <c r="F19" s="2">
-        <v>1297</v>
+        <v>2252</v>
       </c>
       <c r="G19" s="2">
         <v>46</v>
@@ -1244,8 +1232,8 @@
       <c r="I19" s="2">
         <v>-16</v>
       </c>
-      <c r="J19" s="4" t="s">
-        <v>21</v>
+      <c r="J19" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>15</v>
@@ -1253,34 +1241,34 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="D20" s="2">
-        <v>6061</v>
+        <v>4628</v>
       </c>
       <c r="E20" s="2">
-        <v>8286</v>
+        <v>21460</v>
       </c>
       <c r="F20" s="2">
-        <v>-2225</v>
+        <v>-16832</v>
       </c>
       <c r="G20" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H20" s="2">
         <v>30</v>
       </c>
       <c r="I20" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>15</v>
@@ -1288,22 +1276,22 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D21" s="2">
-        <v>9583</v>
+        <v>8901</v>
       </c>
       <c r="E21" s="2">
-        <v>8286</v>
+        <v>21460</v>
       </c>
       <c r="F21" s="2">
-        <v>1297</v>
+        <v>-12559</v>
       </c>
       <c r="G21" s="2">
         <v>46</v>
@@ -1315,7 +1303,7 @@
         <v>-16</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>15</v>
@@ -1323,34 +1311,34 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D22" s="2">
-        <v>6157</v>
+        <v>8901</v>
       </c>
       <c r="E22" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F22" s="2">
-        <v>-15304</v>
+        <v>-12559</v>
       </c>
       <c r="G22" s="2">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H22" s="2">
         <v>30</v>
       </c>
       <c r="I22" s="2">
-        <v>7</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>14</v>
+        <v>-16</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>15</v>
@@ -1358,22 +1346,22 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D23" s="2">
-        <v>8901</v>
+        <v>9583</v>
       </c>
       <c r="E23" s="2">
-        <v>21461</v>
+        <v>7331</v>
       </c>
       <c r="F23" s="2">
-        <v>-12560</v>
+        <v>2252</v>
       </c>
       <c r="G23" s="2">
         <v>46</v>
@@ -1393,22 +1381,22 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="D24" s="2">
-        <v>8901</v>
+        <v>8095</v>
       </c>
       <c r="E24" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F24" s="2">
-        <v>-12560</v>
+        <v>-13365</v>
       </c>
       <c r="G24" s="2">
         <v>46</v>
@@ -1419,8 +1407,8 @@
       <c r="I24" s="2">
         <v>-16</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>14</v>
+      <c r="J24" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>15</v>
@@ -1428,22 +1416,22 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D25" s="2">
-        <v>9583</v>
+        <v>8901</v>
       </c>
       <c r="E25" s="2">
-        <v>7331</v>
+        <v>21460</v>
       </c>
       <c r="F25" s="2">
-        <v>2252</v>
+        <v>-12559</v>
       </c>
       <c r="G25" s="2">
         <v>46</v>
@@ -1455,7 +1443,7 @@
         <v>-16</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>15</v>
@@ -1463,34 +1451,34 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D26" s="2">
-        <v>6157</v>
+        <v>8901</v>
       </c>
       <c r="E26" s="2">
-        <v>21461</v>
+        <v>21460</v>
       </c>
       <c r="F26" s="2">
-        <v>-15304</v>
+        <v>-12559</v>
       </c>
       <c r="G26" s="2">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H26" s="2">
         <v>30</v>
       </c>
       <c r="I26" s="2">
-        <v>7</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>14</v>
+        <v>-16</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>15</v>
@@ -1498,22 +1486,22 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D27" s="2">
-        <v>8901</v>
+        <v>8095</v>
       </c>
       <c r="E27" s="2">
-        <v>21461</v>
+        <v>8778</v>
       </c>
       <c r="F27" s="2">
-        <v>-12560</v>
+        <v>-683</v>
       </c>
       <c r="G27" s="2">
         <v>46</v>
@@ -1528,391 +1516,6 @@
         <v>14</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D28" s="2">
-        <v>8901</v>
-      </c>
-      <c r="E28" s="2">
-        <v>21461</v>
-      </c>
-      <c r="F28" s="2">
-        <v>-12560</v>
-      </c>
-      <c r="G28" s="2">
-        <v>46</v>
-      </c>
-      <c r="H28" s="2">
-        <v>30</v>
-      </c>
-      <c r="I28" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="2">
-        <v>9583</v>
-      </c>
-      <c r="E29" s="2">
-        <v>7331</v>
-      </c>
-      <c r="F29" s="2">
-        <v>2252</v>
-      </c>
-      <c r="G29" s="2">
-        <v>46</v>
-      </c>
-      <c r="H29" s="2">
-        <v>30</v>
-      </c>
-      <c r="I29" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D30" s="2">
-        <v>6157</v>
-      </c>
-      <c r="E30" s="2">
-        <v>21461</v>
-      </c>
-      <c r="F30" s="2">
-        <v>-15304</v>
-      </c>
-      <c r="G30" s="2">
-        <v>23</v>
-      </c>
-      <c r="H30" s="2">
-        <v>30</v>
-      </c>
-      <c r="I30" s="2">
-        <v>7</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D31" s="2">
-        <v>8901</v>
-      </c>
-      <c r="E31" s="2">
-        <v>21461</v>
-      </c>
-      <c r="F31" s="2">
-        <v>-12560</v>
-      </c>
-      <c r="G31" s="2">
-        <v>46</v>
-      </c>
-      <c r="H31" s="2">
-        <v>30</v>
-      </c>
-      <c r="I31" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D32" s="2">
-        <v>8901</v>
-      </c>
-      <c r="E32" s="2">
-        <v>21461</v>
-      </c>
-      <c r="F32" s="2">
-        <v>-12560</v>
-      </c>
-      <c r="G32" s="2">
-        <v>46</v>
-      </c>
-      <c r="H32" s="2">
-        <v>30</v>
-      </c>
-      <c r="I32" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33" s="2">
-        <v>9583</v>
-      </c>
-      <c r="E33" s="2">
-        <v>7331</v>
-      </c>
-      <c r="F33" s="2">
-        <v>2252</v>
-      </c>
-      <c r="G33" s="2">
-        <v>46</v>
-      </c>
-      <c r="H33" s="2">
-        <v>30</v>
-      </c>
-      <c r="I33" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D34" s="2">
-        <v>6157</v>
-      </c>
-      <c r="E34" s="2">
-        <v>21461</v>
-      </c>
-      <c r="F34" s="2">
-        <v>-15304</v>
-      </c>
-      <c r="G34" s="2">
-        <v>23</v>
-      </c>
-      <c r="H34" s="2">
-        <v>30</v>
-      </c>
-      <c r="I34" s="2">
-        <v>7</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D35" s="2">
-        <v>8901</v>
-      </c>
-      <c r="E35" s="2">
-        <v>21461</v>
-      </c>
-      <c r="F35" s="2">
-        <v>-12560</v>
-      </c>
-      <c r="G35" s="2">
-        <v>46</v>
-      </c>
-      <c r="H35" s="2">
-        <v>30</v>
-      </c>
-      <c r="I35" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D36" s="2">
-        <v>8901</v>
-      </c>
-      <c r="E36" s="2">
-        <v>21461</v>
-      </c>
-      <c r="F36" s="2">
-        <v>-12560</v>
-      </c>
-      <c r="G36" s="2">
-        <v>46</v>
-      </c>
-      <c r="H36" s="2">
-        <v>30</v>
-      </c>
-      <c r="I36" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D37" s="2">
-        <v>8095</v>
-      </c>
-      <c r="E37" s="2">
-        <v>8778</v>
-      </c>
-      <c r="F37" s="2">
-        <v>-683</v>
-      </c>
-      <c r="G37" s="2">
-        <v>46</v>
-      </c>
-      <c r="H37" s="2">
-        <v>30</v>
-      </c>
-      <c r="I37" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J37" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K37" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D38" s="2">
-        <v>8095</v>
-      </c>
-      <c r="E38" s="2">
-        <v>8778</v>
-      </c>
-      <c r="F38" s="2">
-        <v>-683</v>
-      </c>
-      <c r="G38" s="2">
-        <v>46</v>
-      </c>
-      <c r="H38" s="2">
-        <v>30</v>
-      </c>
-      <c r="I38" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J38" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K38" s="2" t="s">
         <v>15</v>
       </c>
     </row>
